--- a/Cell survival results/PL_means.xlsx
+++ b/Cell survival results/PL_means.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -967,16 +967,16 @@
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>1.222952782016584</v>
+        <v>0.1013460046033881</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EXP_2026_3_18</t>
+          <t>EXP_2026_3_19</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>#008000</t>
+          <t>#00FF00</t>
         </is>
       </c>
     </row>
@@ -985,19 +985,19 @@
         <v>2</v>
       </c>
       <c r="B27" t="n">
-        <v>0.1845806471978289</v>
+        <v>0.3784690754291519</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1249804165548859</v>
+        <v>0.07933918414909155</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EXP_2026_3_18</t>
+          <t>EXP_2026_3_19</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>#008000</t>
+          <t>#00FF00</t>
         </is>
       </c>
     </row>
@@ -1006,19 +1006,19 @@
         <v>5</v>
       </c>
       <c r="B28" t="n">
-        <v>0.1087834007272352</v>
+        <v>0.06088083208363006</v>
       </c>
       <c r="C28" t="n">
-        <v>0.09982858817599365</v>
+        <v>0.005639331840591685</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EXP_2026_3_18</t>
+          <t>EXP_2026_3_19</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>#008000</t>
+          <t>#00FF00</t>
         </is>
       </c>
     </row>
@@ -1027,101 +1027,17 @@
         <v>8</v>
       </c>
       <c r="B29" t="n">
-        <v>0.004961294441949571</v>
+        <v>0.004196802589208104</v>
       </c>
       <c r="C29" t="n">
-        <v>0.002948439192109046</v>
+        <v>0.0003500738899969509</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>EXP_2026_3_18</t>
+          <t>EXP_2026_3_19</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
-        <is>
-          <t>#008000</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>0</v>
-      </c>
-      <c r="B30" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0.1013460046033881</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>EXP_2026_3_19</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>#00FF00</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>2</v>
-      </c>
-      <c r="B31" t="n">
-        <v>0.3784690754291519</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0.07933918414909155</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>EXP_2026_3_19</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>#00FF00</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>5</v>
-      </c>
-      <c r="B32" t="n">
-        <v>0.06088083208363006</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0.005639331840591685</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>EXP_2026_3_19</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>#00FF00</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>8</v>
-      </c>
-      <c r="B33" t="n">
-        <v>0.004196802589208104</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0.0003500738899969509</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>EXP_2026_3_19</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
         <is>
           <t>#00FF00</t>
         </is>
